--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -51,15 +51,15 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:31</t>
+    <t xml:space="preserve">2026-09-09 23:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -601,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -627,7 +627,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:29</t>
+    <t xml:space="preserve">2026-09-17 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:23</t>
+    <t xml:space="preserve">2026-09-23 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -601,9 +601,11 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2202</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>2103</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2019</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
@@ -614,9 +616,11 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2103</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>2202</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2019</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
@@ -629,7 +633,9 @@
       <c r="C10" s="2" t="n">
         <v>2302</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="n">
+        <v>2019</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:51</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -715,7 +712,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-02 11:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:24</t>
+    <t xml:space="preserve">2026-10-02 14:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:50</t>
+    <t xml:space="preserve">2026-10-05 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
